--- a/extenbooks/XS1102.xlsx
+++ b/extenbooks/XS1102.xlsx
@@ -447,11 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +463,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Shaikh &amp; Tonak 1987, units=rate</t>
+          <t>S&amp;T 1994 Table N.2 (Candidate A), units=rate</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>(S605+S606)/S617, units=rate</t>
         </is>
       </c>
     </row>
@@ -475,6 +481,11 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>XS1102-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>XS1102-RECON-A</t>
         </is>
       </c>
     </row>
@@ -483,6 +494,9 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.2225052202699261</v>
       </c>
     </row>
@@ -491,6 +505,9 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>0.2245532744035738</v>
       </c>
     </row>
@@ -499,6 +516,9 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0.2288107178678893</v>
       </c>
     </row>
@@ -507,6 +527,9 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0.2223468484419263</v>
       </c>
     </row>
@@ -515,6 +538,9 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0.2162208874724197</v>
       </c>
     </row>
@@ -523,6 +549,9 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>0.2269781967721912</v>
       </c>
     </row>
@@ -531,6 +560,9 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>0.2481864028333846</v>
       </c>
     </row>
@@ -539,6 +571,9 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>0.2375771582989617</v>
       </c>
     </row>
@@ -547,6 +582,9 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>0.2366180138879525</v>
       </c>
     </row>
@@ -555,6 +593,9 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>0.2492937557271894</v>
       </c>
     </row>
@@ -563,6 +604,9 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>0.2484136582982102</v>
       </c>
     </row>
@@ -571,6 +615,9 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>0.2489004978004168</v>
       </c>
     </row>
@@ -579,6 +626,9 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>0.2438879754171271</v>
       </c>
     </row>
@@ -587,6 +637,9 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>0.2440135561002451</v>
       </c>
     </row>
@@ -595,6 +648,9 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.250260300259623</v>
       </c>
     </row>
@@ -603,6 +659,9 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.2699072594212652</v>
       </c>
     </row>
@@ -611,6 +670,9 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>0.2780913630126543</v>
       </c>
     </row>
@@ -619,6 +681,9 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.2777867109289901</v>
       </c>
     </row>
@@ -627,6 +692,9 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.2929976224748904</v>
       </c>
     </row>
@@ -635,6 +703,9 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.3093266299649665</v>
       </c>
     </row>
@@ -643,6 +714,9 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.3080518836748183</v>
       </c>
     </row>
@@ -651,6 +725,9 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>0.3030674310741483</v>
       </c>
     </row>
@@ -659,6 +736,9 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>0.3160429265446712</v>
       </c>
     </row>
@@ -667,6 +747,9 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>0.349265716574609</v>
       </c>
     </row>
@@ -675,6 +758,9 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>0.338405823131824</v>
       </c>
     </row>
@@ -683,6 +769,9 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>0.3286704288555354</v>
       </c>
     </row>
@@ -691,6 +780,9 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>0.3152097831075134</v>
       </c>
     </row>
@@ -699,6 +791,9 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>0.3108805149523937</v>
       </c>
     </row>
@@ -707,6 +802,9 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>0.3241195932170282</v>
       </c>
     </row>
@@ -715,6 +813,9 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>0.3278838780354208</v>
       </c>
     </row>
@@ -723,6 +824,9 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>0.3404573651947289</v>
       </c>
     </row>
@@ -731,6 +835,9 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>0.3448094224773593</v>
       </c>
     </row>
@@ -739,6 +846,9 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>0.329165285261955</v>
       </c>
     </row>
@@ -747,6 +857,9 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>0.331265527655171</v>
       </c>
     </row>
@@ -755,6 +868,9 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>0.3339988452655889</v>
       </c>
     </row>
@@ -763,6 +879,9 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>0.3298620510150963</v>
       </c>
     </row>
@@ -771,6 +890,9 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>0.3242024370933875</v>
       </c>
     </row>
@@ -779,6 +901,9 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>0.3299361805781098</v>
       </c>
     </row>
@@ -793,11 +918,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,56 +1090,120 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shaikh &amp; Tonak 1987</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+          <t>S&amp;T 1994 Table N.2 (Candidate A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>XS1102-RECON-A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(S605+S606)/S617</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t># XS1102 — Social Benefit Rate (S&amp;T 1987)</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t># XS1102 — Social Benefit Rate (S&amp;T 1987)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## D3 book-faithful adoption (2026-07-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>**XS1102-A is now book Table N.2 B1/EC verbatim** (V03 5/5; was reconstruction 0/5 over-count). Reconstruction preserved as **XS1102-RECON-A** (comparison arm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>&gt; Decision: ADOPT NSW Candidate A (Appendix N Tables N.1/N.2 verbatim, 1952-1989) as book-period primary; BEA-API reconstruction becomes the labeled comparison/extension arm. Nothing deleted (.pre_d3 backups + -RECON subseries). See Handoffs/REVIEW_2026-07/D3_REGISTRY_PATCHES.json + D3_DIV_PATCHES.json.</t>
         </is>
       </c>
     </row>
@@ -1491,8 +1680,8 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1533,17 +1722,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S605, BEA_NIPA</t>
+          <t>S605, S606, S617</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1102-COMBINED</t>
+          <t>XS1102-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B_w / EC</t>
+          <t>XS1102 = B_w/EC = (S605 + S606)/S617</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1952": 0.11, "1968": 0.2, "1975": 0.33, "1980": 0.31, "1984": 0.2}</t>
+          <t>{"1952": 0.11, "1964": 0.19, "1971": 0.25, "1980": 0.29, "1989": 0.29}</t>
         </is>
       </c>
     </row>
